--- a/output/pdf_financials_xlsx/ATH.xlsx
+++ b/output/pdf_financials_xlsx/ATH.xlsx
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.303808</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.376164</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.062007</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.125069</v>
+        <v>-0.178739</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.126586</v>
+        <v>-0.249578</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0.035015</v>
@@ -891,28 +891,28 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.003552</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.003958</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.008152</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000817</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.003224</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.011594</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.015541</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.012815</v>
       </c>
     </row>
     <row r="13">
@@ -1626,28 +1626,28 @@
         <v>-0.936734</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.209407</v>
+        <v>-0.212959</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.569657</v>
+        <v>-0.573615</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.246865</v>
+        <v>0.238713</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.457608</v>
+        <v>0.456791</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.572271</v>
+        <v>0.569047</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.037134</v>
+        <v>-0.048728</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.61734</v>
+        <v>0.601799</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.327237</v>
+        <v>0.314422</v>
       </c>
     </row>
     <row r="28">
@@ -1712,28 +1712,28 @@
         <v>-0.875664</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.093972</v>
+        <v>-0.097524</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.407545</v>
+        <v>-0.411503</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.379715</v>
+        <v>0.371563</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.556248</v>
+        <v>0.555431</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.69185</v>
+        <v>0.688626</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.07366399999999999</v>
+        <v>0.06207</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.732393</v>
+        <v>0.716852</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.458539</v>
+        <v>0.445724</v>
       </c>
     </row>
     <row r="30">
@@ -1755,28 +1755,28 @@
         <v>-461.9187533958253</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-12.11043366982018</v>
+        <v>-12.56818981415255</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-51.27003556426666</v>
+        <v>-51.76796045786949</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>45.80939604440573</v>
+        <v>44.82592634593716</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>56.79343858577959</v>
+        <v>56.71002212527172</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>51.27978967763072</v>
+        <v>51.04082741424894</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>6.10472945815388</v>
+        <v>5.143904179349632</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>53.39959009371265</v>
+        <v>52.26647845877569</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>34.65685826210449</v>
+        <v>33.68828712937888</v>
       </c>
     </row>
     <row r="31">
@@ -26238,7 +26238,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -27146,7 +27146,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E282" s="5" t="n">

--- a/output/pdf_financials_xlsx/ATH.xlsx
+++ b/output/pdf_financials_xlsx/ATH.xlsx
@@ -1097,7 +1097,7 @@
         <v>-0.00066</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.063781</v>
+        <v>0.06417100000000001</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0.108377</v>
@@ -1789,7 +1789,7 @@
         <v>-0.4132516013499553</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-21.8923659379623</v>
+        <v>-22.02623061107507</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-13.46050663977306</v>
@@ -5479,10 +5479,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.6013039999999999</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -5835,7 +5835,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>-0.012577</v>
       </c>
       <c r="H123" s="3" t="n">
         <v>0</v>
@@ -5921,7 +5921,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.012577</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>0</v>
@@ -14516,7 +14516,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -19992,7 +19996,11 @@
           <t>Increase in long-term deposit (Note 24)</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -22478,7 +22486,11 @@
           <t>Deferred income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -23682,7 +23694,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -24582,7 +24598,11 @@
           <t>Proceeds on sale of investments (Note 5)</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -25410,7 +25430,11 @@
           <t>Deferred income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E257" s="5" t="n">
         <v>-0.035791</v>
       </c>
@@ -33386,7 +33410,11 @@
           <t>Deferred income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -34502,7 +34530,11 @@
           <t>Deferred income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -35480,7 +35512,11 @@
           <t>Deferred income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E394" s="5" t="n">
         <v>-0.035791</v>
       </c>
